--- a/templates/RTG_data_templates.xlsx
+++ b/templates/RTG_data_templates.xlsx
@@ -6445,7 +6445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6479,6 +6479,131 @@
       <c r="E1" s="4" t="inlineStr">
         <is>
           <t>ReceivedOn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SAMPLE-A1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2027-03-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SAMPLE-A2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SAMPLE-B1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2027-06-30</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SAMPLE-D1</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SAMPLE-E1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2027-01-31</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>

--- a/templates/RTG_data_templates.xlsx
+++ b/templates/RTG_data_templates.xlsx
@@ -6095,7 +6095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6111,26 +6111,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FM Raw Material</t>
+          <t>FM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
-        <is>
-          <t>FM Sinter</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FM Blast Furnace</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
         <is>
           <t>RTG</t>
         </is>

--- a/templates/RTG_data_templates.xlsx
+++ b/templates/RTG_data_templates.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -584,6 +584,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -637,6 +638,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>MadeFrom</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -675,6 +681,7 @@
           <t>Replace with real data</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -713,6 +720,7 @@
           <t>Replace with real data</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -751,6 +759,7 @@
           <t>Replace with real data</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
